--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-06-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£11.04£9.20</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£12.68£10.57</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£16.26£13.55</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£16.54£13.78</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£21.18£17.65</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£22.88£19.06</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£23.21£19.34</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£26.46£22.05</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£28.96£24.13</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£28.26£23.55</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£34.66£28.88</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£42.27£35.22</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£43.26£36.05</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£43.05£35.88</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>£720.42£600.35</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>£904.42£753.68</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£29.43£24.53</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£36.29£30.24</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£39.41£32.84</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£43.97£36.64</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>£44.65£37.21</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>£48.23£40.19</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>£44.24£36.87</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '73.3361.11'</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '80.0066.67'</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '75.8363.19'</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
